--- a/HI02H11_L03_S02/VO_Manifest.xlsx
+++ b/HI02H11_L03_S02/VO_Manifest.xlsx
@@ -9,9 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VO Manifest" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'VO Manifest'!$A$1:$B$56</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,16 +26,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Nirmala UI"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
       <sz val="11"/>
     </font>
     <font>
-      <sz val="12"/>
+      <name val="Nirmala UI"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -49,7 +45,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
+        <fgColor rgb="002F5597"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,22 +58,30 @@
       <diagonal/>
     </border>
     <border>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -444,14 +448,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="118" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Audio ID</t>
@@ -469,662 +473,973 @@
           <t>vo_landing</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>नमस्ते दोस्त! मैं हूँ स्विफ्टी, आइए आज हम शब्दों की जोड़ियाँ बनाते हैं। जैसे— मोर-मोरनी।</t>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>नमस्ते दोस्त! मैं हूँ swiftee, आइए आज हम शब्दों की जोड़ियाँ बनाते हैं। जैसे- मोर-मोरनी</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>vo_poem_intro</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>आइए आज हम एक कविता सुनते हैं— जंगल का मेला।</t>
+          <t>vo_pt_tutorial</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ध्यान से देखिए और मेरे साथ जानिए। चलिए, शुरू करें!</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>vo_poem_01</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>जंगल में एक मेला आया, रंग-बिरंगा खूब सजाया।</t>
+          <t>vo_bridge_lost</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>ये कविता सुनकर मुझे तो बहुत मज़ा आया, लेकिन मेले में भीड़ की वजह से सभी जोड़ियाँ बिछड़ गईं। आइए साथ मिलकर सभी जोड़ियाँ ढूँढ़ते हैं।</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>vo_poem_02</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>शेर आया, शेरनी आई, दोनों ने मिलकर धूम मचाई।</t>
+          <t>vo_pt_guided</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>बहुत बढ़िया! अब हम साथ मिलकर शुरू करते हैं। चलिए, साथ में करें!</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>vo_poem_03</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>मोर पंख रंगीन फैलाए, मोरनी संग ठुमके लगाए।</t>
+          <t>vo_pt_practice</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>वाह! अब आपकी बारी।</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>vo_poem_04</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>घोड़ा आया धूल उड़ाए, घोड़ी पीछे दौड़ी आए।</t>
+          <t>vo_poem_01</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>आइए आज हम एक कविता सुनते हैं— जंगल का मेला। जंगल में एक मेला आया, रंग-बिरंगा खूब सजाया।</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>vo_poem_05</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>बकरा बोला— “में-में-में!” बकरी बोली— “साथ चलें!”</t>
+          <t>vo_poem_02</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>शेर आया, शेरनी आई, दोनों ने मिलकर धूम मचाई।</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>vo_poem_06</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>बंदर लाया लाल गुब्बारा, बंदरिया बोली कितना प्यारा!</t>
+          <t>vo_poem_03</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>मोर पंख रंगीन फैलाए, मोरनी संग ठुमके लगाए।</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>vo_poem_07</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>मुर्गा बोला— “कुकड़ू-कूँ!” मुर्गी बोली— “क्या खाऊँ!”</t>
+          <t>vo_poem_04</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>घोड़ा आया धूल उड़ाए, घोड़ी पीछे दौड़ी आए।</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>vo_poem_08</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>बैल ने जब ढोल बजाया, गाय ने भी नाच दिखाया।</t>
+          <t>vo_poem_05</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>बकरा बोला— “में-में-में!” बकरी बोली— “साथ चलें!”</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>vo_poem_09</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>सूरज ढलते शाम हुई, मेले भर में धूम हुई।</t>
+          <t>vo_poem_06</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>बंदर लाया लाल गुब्बारा, बंदरिया बोली कितना प्यारा!</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>vo_bridge_lost</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>क्या आपको कविता सुनकर मज़ा आया? मेले में भीड़ की वजह से सभी जोड़ियाँ बिछड़ गईं। क्या आप सही जोड़ियाँ ढूँढने में मेरी मदद करेंगे? आइए साथ मिलकर ढूँढ़ते हैं।</t>
+          <t>vo_poem_07</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>मुर्गा बोला— “कुकड़ू-कूँ!” मुर्गी बोली— “क्या खाऊँ!”</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>vo_q_sherni</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>यह शेरनी है, इसे इसकी सही जोड़ी से मिलाइए।</t>
+          <t>vo_poem_08</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>बैल ने जब ढोल बजाया, गाय ने भी नाच दिखाया।</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>vo_h1_sherni</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>सोचिए शेरनी मेले में किसके साथ आई थी?</t>
+          <t>vo_poem_09</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>सूरज ढलते शाम हुई, मेले भर में धूम हुई।</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>vo_h2_sherni</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>शेरनी मेले में शेर के साथ आई थी। शेर की तस्वीर पर टैप कीजिए।</t>
+          <t>vo_q_sherni</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>यह शेरनी है, इसे इसकी सही जोड़ी से मिलाइए।</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>vo_correct_pair</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>शाबाश! आपने सही जोड़ी मिला दी।</t>
+          <t>vo_h1_sherni</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>सोचिए शेरनी मेले में किसके साथ आई थी?</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>vo_q_mor</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>यह मोर है, इसे इसकी सही जोड़ी से मिलाइए।</t>
+          <t>vo_h2_sherni</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>शेरनी मेले में शेर के साथ आई थी। शेर के चित्र पर टैप कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>vo_h1_mor</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>सोचिए मोर मेले में किसके साथ आया था?</t>
+          <t>vo_correct_pair</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>शाबाश! आपने सही जोड़ी मिला दी।</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>vo_h2_mor</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>मोर मेले में मोरनी के साथ आया था। मोरनी की तस्वीर पर टैप कीजिए।</t>
+          <t>vo_name_bail</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>बैल</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>vo_q_bakri</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>यह किसके साथ मेले में आई थी? बकरी</t>
+          <t>vo_name_sher</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>शेर</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>vo_h1_word</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>फिर से कोशिश कीजिए, सही शब्द पहचानिए।</t>
+          <t>vo_name_ghoda</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>घोड़ा</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>vo_h2_bakri</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>यह बकरा है, बकरी-बकरे के साथ मेले में आई थी, इसपर टैप कीजिए।</t>
+          <t>vo_q_mor</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>यह मोर है, इसे इसकी सही जोड़ी से मिलाइए।</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>vo_q_ghoda</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>यह किसके साथ मेले में आया था? घोड़ा</t>
+          <t>vo_h1_mor</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>सोचिए मोर मेले में किसके साथ आया था?</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>vo_h2_ghoda</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>यह घोड़ी है, घोड़ा-घोड़ी के साथ मेले में आया था, इसपर टैप कीजिए।</t>
+          <t>vo_h2_mor</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>मोर मेले में मोरनी के साथ आया था। मोरनी के चित्र पर टैप कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>vo_h1_pair</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>फिर से कोशिश कीजिए, सही जोड़ी पहचानिए।</t>
+          <t>vo_name_morni</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>मोरनी</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>vo_h2_bandar</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>यह बंदर है, इसे बंदरिया से मिलाएंगे। बंदरिया की तसवीर पर टैप कीजिए।</t>
+          <t>vo_name_murgi</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>मुर्गी</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>vo_h2_murga</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>यह मुर्गा है, इसे मुर्गी से मिलाएंगे। मुर्गी की तसवीर पर टैप कीजिए।</t>
+          <t>vo_name_bandariya</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>बंदरिया</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>vo_h2_bail</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>यह बैल है, इसे गाय से मिलाएंगे। गाय की तसवीर पर टैप कीजिए।</t>
+          <t>vo_q_bakri</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>बकरी मेले में किसके साथ आई थी?</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>vo_correct_pairs</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>शाबाश! आपने सभी सही जोड़ियाँ मिला दीं।</t>
+          <t>vo_h1_word</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>फिर से कोशिश कीजिए, सही शब्द पहचानिए।</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>vo_sort_jata_demo</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>बैल मेले में जाता है। गाय मेले में जाती है।</t>
+          <t>vo_h2_bakri</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>यह बकरा है, बकरी-बकरे के साथ मेले में आई थी, इसपर टैप कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>vo_sort_jata_rule</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>इसी तरह हर जानवर के शब्द का वाक्य बनाकर देखिए, जिन वाक्यों के अंत में जाता है आता है उन्हें जाता है वाले डब्बे में और जिन वाक्यों के अंत में जाती है आता है उन्हें जाती है वाले डब्बे में रखिए।</t>
+          <t>vo_name_sherni</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>शेरनी</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>vo_sort_jata_h1</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>वाक्य बनाकर देखिए, यह जानवर जाता है या जाती है।</t>
+          <t>vo_name_bakra</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>बकरा</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>vo_h2_sher_jata</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>यह शेर है, शेर जाता है। इसे जाता है वाले डब्बे में रखेंगे।</t>
+          <t>vo_q_ghoda</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>घोड़ा मेले में किसके साथ आया था?</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>vo_h2_sherni_jati</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>यह शेरनी है, शेरनी जाती है। इसे जाती है वाले डब्बे में रखेंगे।</t>
+          <t>vo_h2_ghoda</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>यह घोड़ी है, घोड़ा-घोड़ी के साथ मेले में आया था, इसपर टैप कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>vo_h2_murga_jata</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>यह मुर्गा है, मुर्गा जाता है। इसे जाता है वाले डब्बे में रखेंगे।</t>
+          <t>vo_name_gaay</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>गाय</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>vo_h2_murgi_jati</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>यह मुर्गी है, मुर्गी जाती है। इसे जाती है वाले डब्बे में रखेंगे।</t>
+          <t>vo_name_ghodi</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>घोड़ी</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>vo_q_bail</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>यह बैल है, इसे इसकी सही जोड़ी से मिलाइए।</t>
+          <t>vo_sort_jata_demo</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>बैल मेले में जाता है। गाय मेले में जाती है।</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>vo_h1_bail</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>सोचिए बैल मेले में किसके साथ आया था?</t>
+          <t>vo_sort_jata_h1</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>वाक्य बनाकर देखिए, यह जानवर जाता है या जाती है।</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>vo_h2_bail_gaay</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>बैल मेले में गाय के साथ आया था। गाय की तस्वीर पर टैप कीजिए।</t>
+          <t>vo_sort_jata_rule</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>इसी तरह हर जानवर के शब्द का वाक्य बनाकर देखिए। जिन वाक्यों के अंत में जाता है आता है उन्हें जाता है वाले डब्बे में, और जिन वाक्यों के अंत में जाती है आता है उन्हें जाती है वाले डब्बे में रखिए।</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>vo_q_sentence</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>सही शब्द चुनकर वाक्य पूरा कीजिए। बकरा घास खा… रहा है या रही है?</t>
+          <t>vo_h2_sher_jata</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>यह शेर है, शेर जाता है। इसे जाता है वाले डब्बे में रखेंगे।</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>vo_h1_sentence</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>हम वाक्य में बोलते हैं— बकरा घास खा रहा है। रहा है पर टैप कीजिए और वाक्य पूरा कीजिए।</t>
+          <t>vo_h2_sherni_jati</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>यह शेरनी है, शेरनी जाती है। इसे जाती है वाले डब्बे में रखेंगे।</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>vo_c_sentence</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>शाबाश! सही वाक्य है— बकरा घास खा रहा है।</t>
+          <t>vo_name_murga</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>मुर्गा</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>vo_h2_bakra</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>यह बकरा है, इसे बकरी से मिलाएंगे। बकरी की तसवीर पर टैप कीजिए।</t>
+          <t>vo_h2_murga_jata</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>यह मुर्गा है, मुर्गा जाता है। इसे जाता है वाले डब्बे में रखेंगे।</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>vo_h2_mor_p</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>यह मोर है, इसे मोरनी से मिलाएंगे। मोरनी की तसवीर पर टैप कीजिए।</t>
+          <t>vo_h2_murgi_jati</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>यह मुर्गी है, मुर्गी जाती है। इसे जाती है वाले डब्बे में रखेंगे।</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>vo_h2_ghoda_p</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>यह घोड़ा है, इसे घोड़ी से मिलाएंगे। घोड़ी की तसवीर पर टैप कीजिए।</t>
+          <t>vo_match_pairs</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>हर जानवर को उसकी सही जोड़ी से मिलाइए।</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>vo_gate_rule</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>यहाँ दो गेट हैं, एक पर गया लिखा है और दूसरे पर गई लिखा है। हर जानवर के नाम से वाक्य बनाकर देखिए — जिनके अंत में गया आता है उन्हें गया वाले गेट से और जिनके अंत में गई आता है उन्हें गई वाले गेट से मेले में भेजिए। जैसे— मुर्गा मेले में गया। इसे गया वाले गेट से भेजिए। अब आप खुद करिए।</t>
+          <t>vo_h1_pair</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>फिर से कोशिश कीजिए, सही जोड़ी पहचानिए।</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>vo_gate_h1</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>सोचिए इस जानवर के नाम से वाक्य बनाने पर गया आता है या गई?</t>
+          <t>vo_correct_pairs</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>शाबाश! आपने सभी सही जोड़ियाँ मिला दीं।</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>vo_h2_bandar_gaya</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>यह बंदर है, बंदर मेले में गया। इसे गया वाले गेट से अंदर भेजेंगे।</t>
+          <t>vo_name_bandar</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>बंदर</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>vo_h2_bandariya_gai</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>यह बंदरिया है, बंदरिया मेले में गई। इसे गई वाले गेट से अंदर भेजेंगे।</t>
+          <t>vo_h2_bandar</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>यह बंदर है, इसे बंदरिया से मिलाएंगे। बंदरिया के चित्र पर टैप कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>vo_h2_murga_gaya</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>यह मुर्गा है, मुर्गा मेले में गया। इसे गया वाले गेट से अंदर भेजेंगे।</t>
+          <t>vo_h2_murga</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>यह मुर्गा है, इसे मुर्गी से मिलाएंगे। मुर्गी के चित्र पर टैप कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>vo_h2_murgi_gai</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>यह मुर्गी है, मुर्गी मेले में गई। इसे गई वाले गेट से अंदर भेजेंगे।</t>
+          <t>vo_h2_bail</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>यह बैल है, इसे गाय से मिलाएंगे। गाय के चित्र पर टैप कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>vo_well_done</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>शाबाश! आपने सभी सही जोड़ियाँ पहचान लीं।</t>
+          <t>vo_q_bail</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>यह बैल है, इसे इसकी सही जोड़ी से मिलाइए।</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>vo_pt_tutorial</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>ध्यान से देखिए और मेरे साथ जानिए। चलिए, शुरू करें!</t>
+          <t>vo_h1_bail</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>सोचिए बैल मेले में किसके साथ आया था?</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>vo_pt_guided</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>बहुत बढ़िया! अब हम साथ मिलकर शुरू करते हैं। चलिए, साथ में करें!</t>
+          <t>vo_h2_bail_gaay</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>बैल मेले में गाय के साथ आया था। गाय के चित्र पर टैप कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>vo_pt_practice</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>वाह! अब आपकी बारी।</t>
+          <t>vo_q_sentence</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>सही शब्द चुनकर वाक्य पूरा कीजिए। बकरा घास खा… रहा है या रही है?</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>vo_h1_sentence</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>हम वाक्य में बोलते हैं— बकरा घास खा रहा है। रहा है पर टैप कीजिए और वाक्य पूरा कीजिए।</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>vo_c_sentence</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>शाबाश! सही वाक्य है— बकरा घास खा रहा है।</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>vo_name_bakri</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>बकरी</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>vo_h2_bakra</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>यह बकरा है, इसे बकरी से मिलाएंगे। बकरी के चित्र पर टैप कीजिए।</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>vo_name_mor</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>मोर</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>vo_h2_mor_p</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>यह मोर है, इसे मोरनी से मिलाएंगे। मोरनी के चित्र पर टैप कीजिए।</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>vo_h2_ghoda_p</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>यह घोड़ा है, इसे घोड़ी से मिलाएंगे। घोड़ी के चित्र पर टैप कीजिए।</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>vo_gate_rule</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>यहाँ दो गेट हैं, एक पर गया लिखा है और दूसरे पर गई लिखा है। हर जानवर के नाम से वाक्य बनाकर देखिए — जिनके अंत में गया आता है उन्हें गया वाले गेट से और जिनके अंत में गई आता है उन्हें गई वाले गेट से मेले में भेजिए। जैसे— मुर्गा मेले में गया। इसे गया वाले गेट से भेजिए। अब आप खुद करिए।</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>vo_gate_h1</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>सोचिए इस जानवर के नाम से वाक्य बनाने पर गया आता है या गई?</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>vo_h2_murga_gaya</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>यह मुर्गा है, मुर्गा मेले में गया। इसे गया वाले गेट से अंदर भेजेंगे।</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>vo_gate_done_murga</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>मुर्गा मेले में गया।</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>vo_h2_murgi_gai</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>यह मुर्गी है, मुर्गी मेले में गई। इसे गई वाले गेट से अंदर भेजेंगे।</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>vo_gate_done_murgi</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>मुर्गी मेले में गई।</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>vo_h2_bakra_gaya</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>यह बकरा है, बकरा मेले में गया। इसे गया वाले गेट से अंदर भेजेंगे।</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>vo_gate_done_bakra</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>बकरा मेले में गया।</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>vo_h2_bakri_gai</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>यह बकरी है, बकरी मेले में गई। इसे गई वाले गेट से अंदर भेजेंगे।</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>vo_gate_done_bakri</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>बकरी मेले में गई।</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>vo_h2_bandar_gaya</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>यह बंदर है, बंदर मेले में गया। इसे गया वाले गेट से अंदर भेजेंगे।</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>vo_gate_done_bandar</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>बंदर मेले में गया।</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>vo_h2_bandariya_gai</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>यह बंदरिया है, बंदरिया मेले में गई। इसे गई वाले गेट से अंदर भेजेंगे।</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>vo_gate_done_bandariya</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>बंदरिया मेले में गई।</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>vo_h2_sher_gaya</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>यह शेर है, शेर मेले में गया। इसे गया वाले गेट से अंदर भेजेंगे।</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>vo_gate_done_sher</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>शेर मेले में गया।</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>vo_h2_sherni_gai</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>यह शेरनी है, शेरनी मेले में गई। इसे गई वाले गेट से अंदर भेजेंगे।</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>vo_gate_done_sherni</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>शेरनी मेले में गई।</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>vo_well_done</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>शाबाश! आपने सभी सही जोड़ियाँ पहचान लीं।</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>